--- a/feedback_surveys/027_local_business_review_request--feedback_surveys.xlsx
+++ b/feedback_surveys/027_local_business_review_request--feedback_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Email Hint</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>review_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>Review 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>rating</t>
+          <t>rating_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>rating</t>
+          <t>Rating 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1106,8 +1106,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'good'}</t>
+          <t>good</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'bad'}</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'bad'}</t>
+          <t>bad</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'very_bad'}</t>
+          <t>very_bad</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'very_bad'}</t>
+          <t>very bad</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'positive'}</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'positive'}</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'negative'}</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'negative'}</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'fast'}</t>
+          <t>fast</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'fast'}</t>
+          <t>fast</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'average'}</t>
+          <t>average</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'slow'}</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'slow'}</t>
+          <t>slow</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'good'}</t>
+          <t>good</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'bad'}</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'bad'}</t>
+          <t>bad</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'low'}</t>
+          <t>low</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'average'}</t>
+          <t>average</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'high'}</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'restaurant'}</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'restaurant'}</t>
+          <t>restaurant</t>
         </is>
       </c>
     </row>
@@ -1475,12 +1475,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'shop'}</t>
+          <t>shop</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'shop'}</t>
+          <t>shop</t>
         </is>
       </c>
     </row>
@@ -1492,12 +1492,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'salon'}</t>
+          <t>salon</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'salon'}</t>
+          <t>salon</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1509,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'local'}</t>
+          <t>local</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'local'}</t>
+          <t>local</t>
         </is>
       </c>
     </row>
@@ -1543,12 +1543,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'online'}</t>
+          <t>online</t>
         </is>
       </c>
     </row>
@@ -1560,12 +1560,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'google'}</t>
+          <t>google</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'google'}</t>
+          <t>google</t>
         </is>
       </c>
     </row>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'yelp'}</t>
+          <t>yelp</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'yelp'}</t>
+          <t>yelp</t>
         </is>
       </c>
     </row>
@@ -1594,12 +1594,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'facebook'}</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'facebook'}</t>
+          <t>facebook</t>
         </is>
       </c>
     </row>
@@ -1611,12 +1611,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'instagram'}</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'instagram'}</t>
+          <t>instagram</t>
         </is>
       </c>
     </row>
